--- a/Capstone_Project/09_Project_Management_Evidence/Group-3_Project_Schedule_and_Sprint_Backlog.xlsx
+++ b/Capstone_Project/09_Project_Management_Evidence/Group-3_Project_Schedule_and_Sprint_Backlog.xlsx
@@ -17,9 +17,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="dd mmm yyyy"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd mmm yyyy"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -89,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -99,10 +98,13 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -490,6 +492,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -563,10 +566,10 @@
           <t>Willem Gerber</t>
         </is>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="7" t="n">
         <v>46311</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="7" t="n">
         <v>46314</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -609,10 +612,10 @@
           <t>Willem Gerber</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="7" t="n">
         <v>46311</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="7" t="n">
         <v>46314</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -655,10 +658,10 @@
           <t>Willem Gerber</t>
         </is>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="7" t="n">
         <v>46311</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="7" t="n">
         <v>46314</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -701,10 +704,10 @@
           <t>Willem Gerber</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="7" t="n">
         <v>46311</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="7" t="n">
         <v>46314</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -747,10 +750,10 @@
           <t>Willem Gerber</t>
         </is>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="7" t="n">
         <v>46311</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="7" t="n">
         <v>46314</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -793,10 +796,10 @@
           <t>Willem Gerber</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="7" t="n">
         <v>46311</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="7" t="n">
         <v>46314</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -839,10 +842,10 @@
           <t>All members</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="7" t="n">
         <v>46310</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="7" t="n">
         <v>46314</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -885,10 +888,10 @@
           <t>Willem Gerber</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="7" t="n">
         <v>46315</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="7" t="n">
         <v>46315</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -931,10 +934,10 @@
           <t>Lebohang Tlaitlai</t>
         </is>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="7" t="n">
         <v>46316</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="7" t="n">
         <v>46317</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -977,10 +980,10 @@
           <t>Willem Gerber</t>
         </is>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="7" t="n">
         <v>46316</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="7" t="n">
         <v>46316</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1023,10 +1026,10 @@
           <t>Oscar Khumalo</t>
         </is>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="7" t="n">
         <v>46316</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="7" t="n">
         <v>46316</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1069,10 +1072,10 @@
           <t>Lebohang Tlaitlai</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="7" t="n">
         <v>46316</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="7" t="n">
         <v>46316</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1115,10 +1118,10 @@
           <t>Willem Gerber</t>
         </is>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="7" t="n">
         <v>46316</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="7" t="n">
         <v>46316</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1161,11 +1164,11 @@
           <t>Thomas du Plessis</t>
         </is>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="7" t="n">
         <v>46316</v>
       </c>
-      <c r="F17" s="5" t="n">
-        <v>46318</v>
+      <c r="F17" s="7" t="n">
+        <v>46317</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -1174,15 +1177,15 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Page still to be built</t>
+          <t>Commit c2ecca1 and pull request #6</t>
         </is>
       </c>
     </row>
@@ -1207,10 +1210,10 @@
           <t>Willem Gerber</t>
         </is>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" s="7" t="n">
         <v>46317</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F18" s="7" t="n">
         <v>46317</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1253,10 +1256,10 @@
           <t>Gerhardus van den Berg</t>
         </is>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="7" t="n">
         <v>46315</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" s="7" t="n">
         <v>46317</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1266,15 +1269,15 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Survey shared and answers being collected</t>
+          <t>13 student answers in folder 06 (Group-3_Survey_Responses.xlsx) and Chapter 5 section 5.7</t>
         </is>
       </c>
     </row>
@@ -1296,13 +1299,13 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Development and testing team</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n">
+          <t>Willem Gerber</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n">
         <v>46317</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F20" s="7" t="n">
         <v>46318</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1312,15 +1315,15 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Folder 06 workbooks</t>
+          <t>Folder 06 workbooks and Test Plan (defects fixed and retested)</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1340,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Chapter 5 draft and Chapter 4 sections 4.6 to 4.8</t>
+          <t>Chapter 5 and Chapter 4 sections 4.6 to 4.8</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1345,10 +1348,10 @@
           <t>All members</t>
         </is>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E21" s="7" t="n">
         <v>46317</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F21" s="7" t="n">
         <v>46318</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1358,15 +1361,15 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Week 4 PDF</t>
+          <t>Chapter 5 and Chapter 4 sections 4.6 to 4.9 done</t>
         </is>
       </c>
     </row>
@@ -1391,10 +1394,10 @@
           <t>All members</t>
         </is>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="7" t="n">
         <v>46317</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F22" s="7" t="n">
         <v>46318</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1404,15 +1407,15 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Demo script and video</t>
+          <t>Video recorded (3 minutes) and linked on page 1 and the Demo Script is still to be sent</t>
         </is>
       </c>
     </row>
@@ -1437,10 +1440,10 @@
           <t>Willem Gerber</t>
         </is>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="7" t="n">
         <v>46318</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F23" s="7" t="n">
         <v>46318</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1483,10 +1486,10 @@
           <t>Willem Gerber</t>
         </is>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="7" t="n">
         <v>46319</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="7" t="n">
         <v>46321</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1496,11 +1499,11 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -1529,10 +1532,10 @@
           <t>Lebohang Tlaitlai</t>
         </is>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="7" t="n">
         <v>46319</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F25" s="7" t="n">
         <v>46321</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1542,11 +1545,11 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -1575,10 +1578,10 @@
           <t>Testing team</t>
         </is>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="7" t="n">
         <v>46319</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="F26" s="7" t="n">
         <v>46321</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1621,10 +1624,10 @@
           <t>All members</t>
         </is>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E27" s="7" t="n">
         <v>46319</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="7" t="n">
         <v>46321</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1667,10 +1670,10 @@
           <t>All members</t>
         </is>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E28" s="7" t="n">
         <v>46321</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="F28" s="7" t="n">
         <v>46322</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1713,10 +1716,10 @@
           <t>All members</t>
         </is>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="7" t="n">
         <v>46321</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="7" t="n">
         <v>46323</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1751,7 +1754,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Final dissertation Turnitin check and submission</t>
+          <t>Final dissertation and submission</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1759,10 +1762,10 @@
           <t>Willem Gerber</t>
         </is>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" s="7" t="n">
         <v>46323</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="F30" s="7" t="n">
         <v>46324</v>
       </c>
       <c r="G30" s="2" t="inlineStr">

--- a/Capstone_Project/09_Project_Management_Evidence/Group-3_Project_Schedule_and_Sprint_Backlog.xlsx
+++ b/Capstone_Project/09_Project_Management_Evidence/Group-3_Project_Schedule_and_Sprint_Backlog.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="4" min="1" max="1"/>
@@ -492,7 +492,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -1407,15 +1406,15 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Video recorded (3 minutes) and linked on page 1 and the Demo Script is still to be sent</t>
+          <t>Video recorded and linked on page 1 and the Demo Script and slides are in folder 11</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1426,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Sprint 1</t>
+          <t>Sprint 2</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Compile and submit Week 4</t>
+          <t>Back-end fixes and security check</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1441,10 +1440,10 @@
         </is>
       </c>
       <c r="E23" s="7" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -1453,15 +1452,15 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Group3_Week4.pdf on Teams</t>
+          <t>Fixed routes and access tests</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1477,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Back-end fixes and security check</t>
+          <t>Front-end fixes and polish</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Willem Gerber</t>
+          <t>Lebohang Tlaitlai</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -1494,7 +1493,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1507,7 +1506,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Fixed routes and access tests</t>
+          <t>Fixed pages</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1523,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Front-end fixes and polish</t>
+          <t>User testing with 5 students and 1 lecturer</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Lebohang Tlaitlai</t>
+          <t>Testing team</t>
         </is>
       </c>
       <c r="E25" s="7" t="n">
@@ -1540,20 +1539,20 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Complete</t>
+          <t>Not Started</t>
         </is>
       </c>
       <c r="I25" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Fixed pages</t>
+          <t>Test evidence</t>
         </is>
       </c>
     </row>
@@ -1570,12 +1569,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>User testing with 5 students and 1 lecturer</t>
+          <t>Final Chapter 5 and Chapter 6</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Testing team</t>
+          <t>All members</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -1599,7 +1598,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Test evidence</t>
+          <t>Final chapters</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1615,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Final Chapter 5 and Chapter 6</t>
+          <t>Demo data demo laptop and backup video</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1625,14 +1624,14 @@
         </is>
       </c>
       <c r="E27" s="7" t="n">
-        <v>46319</v>
+        <v>46321</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1645,7 +1644,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Final chapters</t>
+          <t>Demo ready</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1661,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Demo data demo laptop and backup video</t>
+          <t>Final slides and practice runs</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1674,7 +1673,7 @@
         <v>46321</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -1691,7 +1690,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Demo ready</t>
+          <t>Slides</t>
         </is>
       </c>
     </row>
@@ -1708,23 +1707,23 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Final slides and practice runs</t>
+          <t>Final dissertation and submission</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>All members</t>
+          <t>Willem Gerber</t>
         </is>
       </c>
       <c r="E29" s="7" t="n">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1737,55 +1736,21 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Slides</t>
+          <t>Final submission and live demo 29 Oct</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>T27</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Sprint 2</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Final dissertation and submission</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Willem Gerber</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>46324</v>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>Not Started</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>Final submission and live demo 29 Oct</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="n"/>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
+      <c r="J30" s="2" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -1990,18 +1955,6 @@
       <c r="H47" s="2" t="n"/>
       <c r="I47" s="2" t="n"/>
       <c r="J47" s="2" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="n"/>
-      <c r="F48" s="2" t="n"/>
-      <c r="G48" s="2" t="n"/>
-      <c r="H48" s="2" t="n"/>
-      <c r="I48" s="2" t="n"/>
-      <c r="J48" s="2" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:J103"/>

--- a/Capstone_Project/09_Project_Management_Evidence/Group-3_Project_Schedule_and_Sprint_Backlog.xlsx
+++ b/Capstone_Project/09_Project_Management_Evidence/Group-3_Project_Schedule_and_Sprint_Backlog.xlsx
@@ -1590,15 +1590,15 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Final chapters</t>
+          <t>Chapter 6 written on 26 Oct and the final Chapter 5 still to do</t>
         </is>
       </c>
     </row>

--- a/Capstone_Project/09_Project_Management_Evidence/Group-3_Project_Schedule_and_Sprint_Backlog.xlsx
+++ b/Capstone_Project/09_Project_Management_Evidence/Group-3_Project_Schedule_and_Sprint_Backlog.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Willem Gerber</t>
+          <t>All members</t>
         </is>
       </c>
       <c r="E4" s="7" t="n">
@@ -608,7 +608,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Willem Gerber</t>
+          <t>All members</t>
         </is>
       </c>
       <c r="E5" s="7" t="n">
@@ -654,7 +654,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Willem Gerber</t>
+          <t>All members</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
@@ -700,7 +700,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Willem Gerber</t>
+          <t>All members</t>
         </is>
       </c>
       <c r="E7" s="7" t="n">
@@ -746,7 +746,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Willem Gerber</t>
+          <t>Gerhardus van den Berg</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
@@ -1523,19 +1523,19 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>User testing with 5 students and 1 lecturer</t>
+          <t>User testing with 4 students and 2 lecturers</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Testing team</t>
+          <t>Oscar Khumalo</t>
         </is>
       </c>
       <c r="E25" s="7" t="n">
-        <v>46319</v>
+        <v>46323</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>46321</v>
+        <v>46323</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
@@ -1544,15 +1544,15 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Test evidence</t>
+          <t>Google Form results on 28 Oct and Chapter 5 section 5.6</t>
         </is>
       </c>
     </row>
@@ -1590,15 +1590,15 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Chapter 6 written on 26 Oct and the final Chapter 5 still to do</t>
+          <t>Final Chapters 5 and 6 in Group3_Final_Dissertation (folder 08)</t>
         </is>
       </c>
     </row>
@@ -1636,15 +1636,15 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I27" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Demo ready</t>
+          <t>Demo data loaded, MySQL and booking emails checked on the demonstration laptop and backup video ready</t>
         </is>
       </c>
     </row>
@@ -1682,15 +1682,15 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Slides</t>
+          <t>CampusBook_Group3_Presentation.pptx in folder 11 and practice run on 28 Oct</t>
         </is>
       </c>
     </row>
@@ -1728,15 +1728,15 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Not Started</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Final submission and live demo 29 Oct</t>
+          <t>Group3_Final_Dissertation PDF and Word in folder 08 for the 29 Oct submission</t>
         </is>
       </c>
     </row>
